--- a/output/roomself_excel/1725.xlsx
+++ b/output/roomself_excel/1725.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,10 @@
         <v>5140</v>
       </c>
       <c r="E2" t="n">
-        <v>1175</v>
+        <v>680</v>
       </c>
       <c r="F2" t="n">
-        <v>680</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25807</v>
+        <v>357632</v>
       </c>
       <c r="D3" t="n">
-        <v>1312</v>
+        <v>4848</v>
       </c>
       <c r="E3" t="n">
-        <v>131</v>
+        <v>740</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>580</v>
       </c>
     </row>
     <row r="4">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>348840</v>
+        <v>19180</v>
       </c>
       <c r="D6" t="n">
-        <v>4776</v>
+        <v>1108</v>
       </c>
       <c r="E6" t="n">
-        <v>717</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>295830</v>
+        <v>46440</v>
       </c>
       <c r="D7" t="n">
-        <v>4356</v>
+        <v>1752</v>
       </c>
       <c r="E7" t="n">
-        <v>1094</v>
+        <v>258</v>
       </c>
       <c r="F7" t="n">
-        <v>412</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>169807</v>
+        <v>24750</v>
       </c>
       <c r="D8" t="n">
-        <v>3328</v>
+        <v>1260</v>
       </c>
       <c r="E8" t="n">
-        <v>504</v>
+        <v>43</v>
       </c>
       <c r="F8" t="n">
-        <v>392</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4408</v>
+        <v>236864</v>
       </c>
       <c r="D9" t="n">
-        <v>536</v>
+        <v>4208</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1067</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>918</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10370</v>
+        <v>167010</v>
       </c>
       <c r="D10" t="n">
-        <v>924</v>
+        <v>3452</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>569</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20049</v>
+        <v>14111</v>
       </c>
       <c r="D11" t="n">
-        <v>1144</v>
+        <v>960</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4756</v>
+        <v>58941</v>
       </c>
       <c r="D12" t="n">
-        <v>560</v>
+        <v>2040</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20060</v>
+        <v>39200</v>
       </c>
       <c r="D13" t="n">
-        <v>1596</v>
+        <v>1680</v>
       </c>
       <c r="E13" t="n">
-        <v>59</v>
+        <v>234</v>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>311499</v>
+        <v>89628</v>
       </c>
       <c r="D14" t="n">
-        <v>4544</v>
+        <v>2396</v>
       </c>
       <c r="E14" t="n">
-        <v>663</v>
+        <v>332</v>
       </c>
       <c r="F14" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>357632</v>
+        <v>40920</v>
       </c>
       <c r="D15" t="n">
-        <v>4848</v>
+        <v>1652</v>
       </c>
       <c r="E15" t="n">
-        <v>740</v>
+        <v>264</v>
       </c>
       <c r="F15" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>679571</v>
+        <v>282174</v>
       </c>
       <c r="D16" t="n">
-        <v>12380</v>
+        <v>4444</v>
       </c>
       <c r="E16" t="n">
-        <v>1655</v>
+        <v>756</v>
       </c>
       <c r="F16" t="n">
-        <v>1283</v>
+        <v>429</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>58941</v>
+        <v>25807</v>
       </c>
       <c r="D17" t="n">
-        <v>2040</v>
+        <v>1312</v>
       </c>
       <c r="E17" t="n">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>167010</v>
+        <v>348840</v>
       </c>
       <c r="D18" t="n">
-        <v>3452</v>
+        <v>4776</v>
       </c>
       <c r="E18" t="n">
-        <v>1132</v>
+        <v>717</v>
       </c>
       <c r="F18" t="n">
-        <v>495</v>
+        <v>543</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19180</v>
+        <v>295830</v>
       </c>
       <c r="D19" t="n">
-        <v>1108</v>
+        <v>4356</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>46440</v>
+        <v>169807</v>
       </c>
       <c r="D20" t="n">
-        <v>1752</v>
+        <v>3328</v>
       </c>
       <c r="E20" t="n">
-        <v>258</v>
+        <v>504</v>
       </c>
       <c r="F20" t="n">
-        <v>41</v>
+        <v>392</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>201414</v>
+        <v>4408</v>
       </c>
       <c r="D21" t="n">
-        <v>3628</v>
+        <v>536</v>
       </c>
       <c r="E21" t="n">
-        <v>543</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4429</v>
+        <v>10370</v>
       </c>
       <c r="D22" t="n">
-        <v>584</v>
+        <v>924</v>
       </c>
       <c r="E22" t="n">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -928,20 +928,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14111</v>
+        <v>20049</v>
       </c>
       <c r="D23" t="n">
-        <v>960</v>
+        <v>1144</v>
       </c>
       <c r="E23" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -950,20 +950,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>39200</v>
+        <v>4756</v>
       </c>
       <c r="D24" t="n">
-        <v>1680</v>
+        <v>560</v>
       </c>
       <c r="E24" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>44280</v>
+        <v>20060</v>
       </c>
       <c r="D25" t="n">
-        <v>1704</v>
+        <v>1596</v>
       </c>
       <c r="E25" t="n">
-        <v>246</v>
+        <v>59</v>
       </c>
       <c r="F25" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
@@ -994,20 +994,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>89628</v>
+        <v>311499</v>
       </c>
       <c r="D26" t="n">
-        <v>2396</v>
+        <v>4544</v>
       </c>
       <c r="E26" t="n">
-        <v>879</v>
+        <v>663</v>
       </c>
       <c r="F26" t="n">
-        <v>83</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>69549</v>
+        <v>201414</v>
       </c>
       <c r="D27" t="n">
-        <v>2120</v>
+        <v>3628</v>
       </c>
       <c r="E27" t="n">
-        <v>765</v>
+        <v>543</v>
       </c>
       <c r="F27" t="n">
-        <v>137</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28">
@@ -1038,20 +1038,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24750</v>
+        <v>442707</v>
       </c>
       <c r="D28" t="n">
-        <v>1260</v>
+        <v>8636</v>
       </c>
       <c r="E28" t="n">
-        <v>616</v>
+        <v>1126</v>
       </c>
       <c r="F28" t="n">
-        <v>67</v>
+        <v>775</v>
       </c>
     </row>
     <row r="29">
@@ -1064,16 +1064,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>81600</v>
+        <v>4429</v>
       </c>
       <c r="D29" t="n">
-        <v>2288</v>
+        <v>584</v>
       </c>
       <c r="E29" t="n">
-        <v>789</v>
+        <v>295</v>
       </c>
       <c r="F29" t="n">
-        <v>178</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>40920</v>
+        <v>44280</v>
       </c>
       <c r="D30" t="n">
-        <v>1652</v>
+        <v>1704</v>
       </c>
       <c r="E30" t="n">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F30" t="n">
-        <v>200</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31">
@@ -1108,16 +1108,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>14100</v>
+        <v>69549</v>
       </c>
       <c r="D31" t="n">
-        <v>976</v>
+        <v>2120</v>
       </c>
       <c r="E31" t="n">
-        <v>94</v>
+        <v>239</v>
       </c>
       <c r="F31" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
@@ -1130,16 +1130,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>127292</v>
+        <v>81600</v>
       </c>
       <c r="D32" t="n">
-        <v>3072</v>
+        <v>2288</v>
       </c>
       <c r="E32" t="n">
-        <v>242</v>
+        <v>789</v>
       </c>
       <c r="F32" t="n">
-        <v>24</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33">
@@ -1152,16 +1152,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>44044</v>
+        <v>14100</v>
       </c>
       <c r="D33" t="n">
-        <v>1696</v>
+        <v>976</v>
       </c>
       <c r="E33" t="n">
-        <v>242</v>
+        <v>94</v>
       </c>
       <c r="F33" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34">
@@ -1174,16 +1174,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>293862</v>
+        <v>127292</v>
       </c>
       <c r="D34" t="n">
-        <v>4532</v>
+        <v>3072</v>
       </c>
       <c r="E34" t="n">
-        <v>789</v>
+        <v>242</v>
       </c>
       <c r="F34" t="n">
-        <v>432</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35">
@@ -1192,20 +1192,42 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>282174</v>
+        <v>44044</v>
       </c>
       <c r="D35" t="n">
-        <v>4444</v>
+        <v>1696</v>
       </c>
       <c r="E35" t="n">
-        <v>756</v>
+        <v>242</v>
       </c>
       <c r="F35" t="n">
-        <v>429</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>293862</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4532</v>
+      </c>
+      <c r="E36" t="n">
+        <v>789</v>
+      </c>
+      <c r="F36" t="n">
+        <v>432</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/1725.xlsx
+++ b/output/roomself_excel/1725.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>5140</v>
       </c>
-      <c r="E2" t="n">
-        <v>680</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>420</v>
-      </c>
+        <v>635</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>381</v>
+      </c>
+      <c r="J2" t="n">
+        <v>36</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,31 @@
       <c r="D3" t="n">
         <v>4848</v>
       </c>
-      <c r="E3" t="n">
-        <v>740</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>580</v>
-      </c>
+        <v>925</v>
+      </c>
+      <c r="G3" t="n">
+        <v>36</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>508</v>
+      </c>
+      <c r="J3" t="n">
+        <v>36</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +592,23 @@
       <c r="D4" t="n">
         <v>2752</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>307</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>39</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +625,31 @@
       <c r="D5" t="n">
         <v>3432</v>
       </c>
-      <c r="E5" t="n">
-        <v>511</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>361</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="G5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>310</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +666,15 @@
       <c r="D6" t="n">
         <v>1108</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +691,23 @@
       <c r="D7" t="n">
         <v>1752</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>258</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>41</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +724,23 @@
       <c r="D8" t="n">
         <v>1260</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>43</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>31</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +757,15 @@
       <c r="D9" t="n">
         <v>4208</v>
       </c>
-      <c r="E9" t="n">
-        <v>1067</v>
-      </c>
-      <c r="F9" t="n">
-        <v>918</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +782,15 @@
       <c r="D10" t="n">
         <v>3452</v>
       </c>
-      <c r="E10" t="n">
-        <v>569</v>
-      </c>
-      <c r="F10" t="n">
-        <v>347</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +807,23 @@
       <c r="D11" t="n">
         <v>960</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>137</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>38</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +840,23 @@
       <c r="D12" t="n">
         <v>2040</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>177</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>41</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +873,15 @@
       <c r="D13" t="n">
         <v>1680</v>
       </c>
-      <c r="E13" t="n">
-        <v>234</v>
-      </c>
-      <c r="F13" t="n">
-        <v>12</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +898,31 @@
       <c r="D14" t="n">
         <v>2396</v>
       </c>
-      <c r="E14" t="n">
-        <v>332</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G14" t="n">
+        <v>24</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>308</v>
+      </c>
+      <c r="J14" t="n">
+        <v>24</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +939,31 @@
       <c r="D15" t="n">
         <v>1652</v>
       </c>
-      <c r="E15" t="n">
-        <v>264</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>200</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="G15" t="n">
+        <v>35</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>165</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +980,31 @@
       <c r="D16" t="n">
         <v>4444</v>
       </c>
-      <c r="E16" t="n">
-        <v>756</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>429</v>
-      </c>
+        <v>786</v>
+      </c>
+      <c r="G16" t="n">
+        <v>38</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>718</v>
+      </c>
+      <c r="J16" t="n">
+        <v>36</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1021,23 @@
       <c r="D17" t="n">
         <v>1312</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>131</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>39</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1054,31 @@
       <c r="D18" t="n">
         <v>4776</v>
       </c>
-      <c r="E18" t="n">
-        <v>717</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>543</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="G18" t="n">
+        <v>33</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>684</v>
+      </c>
+      <c r="J18" t="n">
+        <v>33</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1095,23 @@
       <c r="D19" t="n">
         <v>4356</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>570</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>33</v>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1128,31 @@
       <c r="D20" t="n">
         <v>3328</v>
       </c>
-      <c r="E20" t="n">
-        <v>504</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>392</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="G20" t="n">
+        <v>33</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>359</v>
+      </c>
+      <c r="J20" t="n">
+        <v>31</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1169,15 @@
       <c r="D21" t="n">
         <v>536</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1194,15 @@
       <c r="D22" t="n">
         <v>924</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1219,15 @@
       <c r="D23" t="n">
         <v>1144</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1244,15 @@
       <c r="D24" t="n">
         <v>560</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1269,23 @@
       <c r="D25" t="n">
         <v>1596</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>59</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>34</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1302,23 @@
       <c r="D26" t="n">
         <v>4544</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
         <v>663</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>31</v>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1335,31 @@
       <c r="D27" t="n">
         <v>3628</v>
       </c>
-      <c r="E27" t="n">
-        <v>543</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>429</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="G27" t="n">
+        <v>33</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>506</v>
+      </c>
+      <c r="J27" t="n">
+        <v>32</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,11 +1376,38 @@
       <c r="D28" t="n">
         <v>8636</v>
       </c>
-      <c r="E28" t="n">
-        <v>1126</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>775</v>
+        <v>370</v>
+      </c>
+      <c r="G28" t="n">
+        <v>38</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1179</v>
+      </c>
+      <c r="J28" t="n">
+        <v>38</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>216</v>
+      </c>
+      <c r="M28" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="29">
@@ -1069,12 +1425,15 @@
       <c r="D29" t="n">
         <v>584</v>
       </c>
-      <c r="E29" t="n">
-        <v>295</v>
-      </c>
-      <c r="F29" t="n">
-        <v>43</v>
-      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1091,12 +1450,23 @@
       <c r="D30" t="n">
         <v>1704</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>246</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>41</v>
       </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1113,12 +1483,23 @@
       <c r="D31" t="n">
         <v>2120</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>239</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>24</v>
       </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1135,12 +1516,23 @@
       <c r="D32" t="n">
         <v>2288</v>
       </c>
-      <c r="E32" t="n">
-        <v>789</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F32" t="n">
-        <v>178</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="G32" t="n">
+        <v>31</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1157,12 +1549,23 @@
       <c r="D33" t="n">
         <v>976</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>94</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>31</v>
       </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1179,12 +1582,23 @@
       <c r="D34" t="n">
         <v>3072</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>242</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>24</v>
       </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1201,12 +1615,23 @@
       <c r="D35" t="n">
         <v>1696</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>242</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>34</v>
       </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1223,11 +1648,38 @@
       <c r="D36" t="n">
         <v>4532</v>
       </c>
-      <c r="E36" t="n">
-        <v>789</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F36" t="n">
-        <v>432</v>
+        <v>402</v>
+      </c>
+      <c r="G36" t="n">
+        <v>24</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>402</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>731</v>
+      </c>
+      <c r="M36" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/1725.xlsx
+++ b/output/roomself_excel/1725.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:Y36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,66 @@
           <t>ExtWallWidth_3</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -535,6 +595,42 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>39</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>214</v>
+      </c>
+      <c r="U2" t="n">
+        <v>36</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -576,6 +672,42 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>369</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>36</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>183</v>
+      </c>
+      <c r="U3" t="n">
+        <v>36</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -609,6 +741,30 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>39</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -650,6 +806,30 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>188</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>34</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -675,6 +855,18 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -708,6 +900,30 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>41</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -741,6 +957,18 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -766,6 +994,18 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -791,6 +1031,18 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -824,6 +1076,30 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>38</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -857,6 +1133,30 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>124</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>41</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -882,6 +1182,18 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -923,6 +1235,18 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -964,6 +1288,18 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1005,6 +1341,54 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>284</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>38</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>152</v>
+      </c>
+      <c r="U16" t="n">
+        <v>38</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>313</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1038,6 +1422,18 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1079,6 +1475,18 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1112,6 +1520,18 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1153,6 +1573,18 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1178,6 +1610,18 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1203,6 +1647,18 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1228,6 +1684,18 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1253,6 +1721,18 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1286,6 +1766,18 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1319,6 +1811,18 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1360,6 +1864,18 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1408,6 +1924,54 @@
       </c>
       <c r="M28" t="n">
         <v>40</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>332</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>38</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
+        <v>97</v>
+      </c>
+      <c r="U28" t="n">
+        <v>38</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>609</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="29">
@@ -1434,6 +1998,18 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1467,6 +2043,30 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>41</v>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1500,6 +2100,18 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1533,6 +2145,18 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1566,6 +2190,18 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1599,6 +2235,18 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1632,6 +2280,18 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1681,6 +2341,18 @@
       <c r="M36" t="n">
         <v>30</v>
       </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
